--- a/data/trending_integrated_20260917_14.xlsx
+++ b/data/trending_integrated_20260917_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.83%</t>
+          <t>'+22.12%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H2" t="n">
         <v>3.52</v>
@@ -610,7 +610,7 @@
         <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>52008691650</v>
+        <v>52478773116</v>
       </c>
       <c r="P2" t="n">
         <v>5140</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21550</v>
+        <v>21600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.11%</t>
+          <t>'+16.38%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -702,7 +702,7 @@
         <v>1.92</v>
       </c>
       <c r="O3" t="n">
-        <v>287133341895</v>
+        <v>288173315245</v>
       </c>
       <c r="P3" t="n">
         <v>59600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4415</v>
+        <v>4400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.97%</t>
+          <t>'+14.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="F4" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="G4" t="n">
-        <v>1302</v>
+        <v>1338</v>
       </c>
       <c r="H4" t="n">
         <v>0.95</v>
@@ -794,7 +794,7 @@
         <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>252225002466</v>
+        <v>255986126568</v>
       </c>
       <c r="P4" t="n">
         <v>6900</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오, 소프트뱅크 등 대기업 인수 및 투자 가능성 언급. 텐버거 기대감 및 거래량 급증.</t>
+          <t>카카오, 소프트뱅크 등 대형 기업의 인수 가능성이 언급되며 10배 상승에 대한 기대감 형성. 거래량 잠김 현상 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '투자', '텐버거']</t>
+          <t>['인수', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F5" t="n">
         <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="H5" t="n">
         <v>8.01</v>
@@ -886,7 +886,7 @@
         <v>8.06</v>
       </c>
       <c r="O5" t="n">
-        <v>94816514517</v>
+        <v>95261982472</v>
       </c>
       <c r="P5" t="n">
         <v>19950</v>
@@ -946,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F6" t="n">
         <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H6" t="n">
         <v>3.71</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21550</v>
+        <v>21500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.68%</t>
+          <t>'+6.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>76494681475</v>
+        <v>77344937200</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1130,13 +1130,13 @@
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>176236936700</v>
+        <v>176883436000</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13425</v>
+        <v>13430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.91%</t>
+          <t>'+3.95%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>58235744230</v>
+        <v>58733414930</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86400</v>
+        <v>86200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+2.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F10" t="n">
         <v>119</v>
       </c>
       <c r="G10" t="n">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>109837820050</v>
+        <v>111412191450</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AP1000 관련 대미 원전 투자 기대감. 공매도 세력과의 대립 및 프로그램 매수 전환.</t>
+          <t>미국 금리 인상 및 대미 투자와 관련된 긍정적 전망 제시. 원전 사업 관련 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '투자', '공매도']</t>
+          <t>['금리인상', '원전', '대미투자']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>255000</v>
+        <v>254750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'+1.70%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G11" t="n">
-        <v>1719</v>
+        <v>1750</v>
       </c>
       <c r="H11" t="n">
         <v>46.52</v>
@@ -1423,28 +1423,28 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>253500</v>
+        <v>250500</v>
       </c>
       <c r="K11" t="n">
-        <v>257000</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>259000</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>252000</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>1942290845000</v>
+        <v>1991513000000</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>77100</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>-678000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 논쟁이 주식 관련 논의를 압도. 특정 정치인 지지 및 비판 의견.</t>
+          <t>정치적 성향에 대한 논쟁만 있을 뿐, 삼성전자 주가에 대한 실질적인 내용은 없음.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '논쟁', '지지']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="G12" t="n">
-        <v>1679</v>
+        <v>1695</v>
       </c>
       <c r="H12" t="n">
         <v>50.2</v>
@@ -1530,7 +1530,7 @@
         <v>50.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3432283399000</v>
+        <v>3519311452000</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1575,175 +1575,175 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16120</v>
+        <v>18630</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.93</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>255</v>
+        <v>92</v>
       </c>
       <c r="F13" t="n">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>1365</v>
+        <v>334</v>
       </c>
       <c r="H13" t="n">
-        <v>4.88</v>
+        <v>10.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16100</v>
+        <v>18570</v>
       </c>
       <c r="K13" t="n">
-        <v>16200</v>
+        <v>18740</v>
       </c>
       <c r="L13" t="n">
-        <v>16750</v>
+        <v>18900</v>
       </c>
       <c r="M13" t="n">
-        <v>15560</v>
+        <v>18510</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>340218913395</v>
+        <v>51878077925</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-749000</v>
+        <v>-287000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>-76000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등에 따른 수혜 기대감과 함께, 물량 소화 및 매집 정황이 포착되며 2만 원대 돌파 전망이 제기됨.</t>
+          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '수혜주', '매집']</t>
+          <t>['대규모계약', 'LNG', '대차해지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8440</v>
+        <v>16150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'+0.31%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.12</v>
+        <v>2.93</v>
       </c>
       <c r="E14" t="n">
-        <v>137</v>
+        <v>259</v>
       </c>
       <c r="F14" t="n">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="G14" t="n">
-        <v>348</v>
+        <v>1366</v>
       </c>
       <c r="H14" t="n">
-        <v>26.54</v>
+        <v>4.88</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8470</v>
+        <v>16100</v>
       </c>
       <c r="K14" t="n">
-        <v>8470</v>
+        <v>16200</v>
       </c>
       <c r="L14" t="n">
-        <v>8510</v>
+        <v>16750</v>
       </c>
       <c r="M14" t="n">
-        <v>8360</v>
+        <v>15560</v>
       </c>
       <c r="N14" t="n">
-        <v>26.66</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>12317178765</v>
+        <v>342306053095</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>1272</v>
       </c>
       <c r="R14" t="n">
-        <v>-335000</v>
+        <v>-749000</v>
       </c>
       <c r="S14" t="n">
-        <v>-5000</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>3분기 실적 부진 및 4분기 전망 불확실성. 높은 부채 비율 및 증권사 목표가 하향 조정.</t>
+          <t>미국 광통신 관련주 급등에 따른 수혜 기대감과 함께, 물량 소화 및 매집 정황이 포착되며 2만 원대 돌파 전망이 제기됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '부채', '전망']</t>
+          <t>['광통신', '수혜주', '매집']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,130 +1752,130 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3465</v>
+        <v>8440</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.85</v>
+        <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="H15" t="n">
-        <v>2.26</v>
+        <v>26.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3520</v>
+        <v>8470</v>
       </c>
       <c r="K15" t="n">
-        <v>3730</v>
+        <v>8470</v>
       </c>
       <c r="L15" t="n">
-        <v>3750</v>
+        <v>8510</v>
       </c>
       <c r="M15" t="n">
-        <v>3420</v>
+        <v>8360</v>
       </c>
       <c r="N15" t="n">
-        <v>3.11</v>
+        <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>5627829133</v>
+        <v>12744207715</v>
       </c>
       <c r="P15" t="n">
-        <v>16110</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>2300</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-317000</v>
+        <v>-335000</v>
       </c>
       <c r="S15" t="n">
-        <v>-9000</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
+          <t>3분기 실적 부진 및 4분기 전망 불확실성. 높은 부채 비율 및 증권사 목표가 하향 조정.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '차익실현']</t>
+          <t>['실적', '부채', '전망']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13300</v>
+        <v>3465</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.56%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.36</v>
+        <v>-0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>89</v>
+        <v>315</v>
       </c>
       <c r="H16" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13530</v>
+        <v>3520</v>
       </c>
       <c r="K16" t="n">
-        <v>14280</v>
+        <v>3730</v>
       </c>
       <c r="L16" t="n">
-        <v>14800</v>
+        <v>3750</v>
       </c>
       <c r="M16" t="n">
-        <v>12960</v>
+        <v>3420</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4</v>
+        <v>3.11</v>
       </c>
       <c r="O16" t="n">
-        <v>82241925670</v>
+        <v>5662272788</v>
       </c>
       <c r="P16" t="n">
-        <v>25700</v>
+        <v>16110</v>
       </c>
       <c r="Q16" t="n">
-        <v>4600</v>
+        <v>2300</v>
       </c>
       <c r="R16" t="n">
-        <v>-80000</v>
+        <v>-317000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>['상장폐지', '폭락', '차익실현']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13730</v>
+        <v>13720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H17" t="n">
         <v>0.01</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>15321746070</v>
+        <v>15449958725</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유가 변동성 및 지정학적 리스크에 따른 주가 등락. 외국인 매수세와 프로그램 매도 공존.</t>
+          <t>유가 변동성에 따른 단기 등락 예측. 후티 반군 관련 지정학적 리스크 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유가', '지정학적 리스크', '외국인']</t>
+          <t>['유가', '후티반군', '지정학적리스크']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,70 +2035,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10210</v>
+        <v>13250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.8</v>
+        <v>1.36</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="H18" t="n">
-        <v>18.42</v>
+        <v>1.76</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10460</v>
+        <v>13530</v>
       </c>
       <c r="K18" t="n">
-        <v>10860</v>
+        <v>14280</v>
       </c>
       <c r="L18" t="n">
-        <v>11150</v>
+        <v>14800</v>
       </c>
       <c r="M18" t="n">
-        <v>10060</v>
+        <v>12960</v>
       </c>
       <c r="N18" t="n">
-        <v>19.22</v>
+        <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>58358124430</v>
+        <v>82408971465</v>
       </c>
       <c r="P18" t="n">
-        <v>22450</v>
+        <v>25700</v>
       </c>
       <c r="Q18" t="n">
-        <v>1760</v>
+        <v>4600</v>
       </c>
       <c r="R18" t="n">
-        <v>-39000</v>
+        <v>-80000</v>
       </c>
       <c r="S18" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18610</v>
+        <v>10240</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.67%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.21</v>
+        <v>-0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>331</v>
+        <v>132</v>
       </c>
       <c r="H19" t="n">
-        <v>10.85</v>
+        <v>18.42</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19320</v>
+        <v>10460</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>10860</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>11150</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>10060</v>
       </c>
       <c r="N19" t="n">
-        <v>10.64</v>
+        <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>50971000000</v>
+        <v>58627431695</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>22450</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1760</v>
       </c>
       <c r="R19" t="n">
-        <v>-287000</v>
+        <v>-39000</v>
       </c>
       <c r="S19" t="n">
-        <v>-76000</v>
+        <v>-5000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['대규모계약', 'LNG', '대차해지']</t>
+          <t>['주포', '시총', '횡보']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4145</v>
+        <v>4135</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.01%</t>
+          <t>'-6.24%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>50433182337</v>
+        <v>50867959780</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_14.xlsx
+++ b/data/trending_integrated_20260917_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1706</v>
+        <v>1699</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.12%</t>
+          <t>'+21.62%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H2" t="n">
         <v>3.52</v>
@@ -610,7 +610,7 @@
         <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>52478773116</v>
+        <v>52784379199</v>
       </c>
       <c r="P2" t="n">
         <v>5140</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21600</v>
+        <v>4545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.38%</t>
+          <t>'+18.36%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>576</v>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>243</v>
       </c>
       <c r="G3" t="n">
-        <v>266</v>
+        <v>1361</v>
       </c>
       <c r="H3" t="n">
-        <v>2.54</v>
+        <v>0.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>18560</v>
+        <v>3840</v>
       </c>
       <c r="K3" t="n">
-        <v>19260</v>
+        <v>4170</v>
       </c>
       <c r="L3" t="n">
-        <v>22950</v>
+        <v>4800</v>
       </c>
       <c r="M3" t="n">
-        <v>18920</v>
+        <v>3990</v>
       </c>
       <c r="N3" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>288173315245</v>
+        <v>263193430083</v>
       </c>
       <c r="P3" t="n">
-        <v>59600</v>
+        <v>6900</v>
       </c>
       <c r="Q3" t="n">
-        <v>1030</v>
+        <v>1738</v>
       </c>
       <c r="R3" t="n">
-        <v>-104000</v>
+        <v>-150000</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
+          <t>카카오, 소프트뱅크 등 대형 기업의 인수 가능성이 언급되며 10배 상승에 대한 기대감 형성. 거래량 잠김 현상 확인.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['CPO', '수주 공시']</t>
+          <t>['인수', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4400</v>
+        <v>21450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.58%</t>
+          <t>'+15.57%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>558</v>
+        <v>95</v>
       </c>
       <c r="F4" t="n">
-        <v>236</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>1338</v>
+        <v>269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.95</v>
+        <v>2.54</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3840</v>
+        <v>18560</v>
       </c>
       <c r="K4" t="n">
-        <v>4170</v>
+        <v>19260</v>
       </c>
       <c r="L4" t="n">
-        <v>4800</v>
+        <v>22950</v>
       </c>
       <c r="M4" t="n">
-        <v>3990</v>
+        <v>18920</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>255986126568</v>
+        <v>289109711245</v>
       </c>
       <c r="P4" t="n">
-        <v>6900</v>
+        <v>59600</v>
       </c>
       <c r="Q4" t="n">
-        <v>1738</v>
+        <v>1030</v>
       </c>
       <c r="R4" t="n">
-        <v>-150000</v>
+        <v>-104000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오, 소프트뱅크 등 대형 기업의 인수 가능성이 언급되며 10배 상승에 대한 기대감 형성. 거래량 잠김 현상 확인.</t>
+          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '소프트뱅크', '텐버거']</t>
+          <t>['CPO', '수주 공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3820</v>
+        <v>3825</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.14%</t>
+          <t>'+9.29%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="H5" t="n">
         <v>8.01</v>
@@ -886,7 +886,7 @@
         <v>8.06</v>
       </c>
       <c r="O5" t="n">
-        <v>95261982472</v>
+        <v>95601681182</v>
       </c>
       <c r="P5" t="n">
         <v>19950</v>
@@ -946,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H6" t="n">
         <v>3.71</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>코다코 부채 언급하며 비교. 개미 물량 이탈 시 100원대 회복 가능성 언급. 300원 이상 상승 기대 및 제2 대한광통신 가능성 제기. 지분 매수 공시 부재 및 거래량 부진.</t>
+          <t>부채 규모와 거래 규칙 변경에 대한 언급. 100원 돌파 및 300원 이상 상승에 대한 기대. 회사 문제 없음에도 걱정하는 시각에 대한 반론. 방산용 AR 디스플레이 양산 협력 신사업 발표.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['거래량', '개미', '공시']</t>
+          <t>['신사업', 'AR 디스플레이', '양산 협력']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21500</v>
+        <v>21400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.44%</t>
+          <t>'+5.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
         <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>77344937200</v>
+        <v>78674603025</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1079,14 +1079,14 @@
         <v>18440</v>
       </c>
       <c r="R7" t="n">
-        <v>1632000</v>
+        <v>1852000</v>
       </c>
       <c r="S7" t="n">
-        <v>191000</v>
+        <v>227000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>FDCT 수주 기대감 및 나스닥 반등에 따른 상승 전망. 장기 보유 및 분할 매수 의견.</t>
+          <t>나스닥 반등과 연계된 긍정적 전망. 금리 인상에도 불구하고 장기 보유 시 수익 기대. 공매도 세력에 대한 경계와 함께 수주 가능성 언급. 60일선 돌파 및 추세 전환 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FDCT', '수주', '나스닥']</t>
+          <t>['추세 전환', '공매도', '수주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1136,7 +1136,7 @@
         <v>83</v>
       </c>
       <c r="G8" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>176883436000</v>
+        <v>177561300220</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1171,7 +1171,7 @@
         <v>3500</v>
       </c>
       <c r="R8" t="n">
-        <v>-18000</v>
+        <v>-26000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13430</v>
+        <v>13400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+3.72%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>58733414930</v>
+        <v>59195616790</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86200</v>
+        <v>85800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.86%</t>
+          <t>'+2.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F10" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G10" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>111412191450</v>
+        <v>114234734050</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1355,10 +1355,10 @@
         <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-92000</v>
+        <v>-95000</v>
       </c>
       <c r="S10" t="n">
-        <v>21000</v>
+        <v>44000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254750</v>
+        <v>16140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.70%</t>
+          <t>'+0.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>260</v>
       </c>
       <c r="F11" t="n">
-        <v>451</v>
+        <v>142</v>
       </c>
       <c r="G11" t="n">
-        <v>1750</v>
+        <v>1380</v>
       </c>
       <c r="H11" t="n">
-        <v>46.52</v>
+        <v>4.88</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250500</v>
+        <v>16100</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>16750</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>15560</v>
       </c>
       <c r="N11" t="n">
-        <v>46.56</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>1991513000000</v>
+        <v>343407479465</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-678000</v>
+        <v>-749000</v>
       </c>
       <c r="S11" t="n">
-        <v>-191000</v>
+        <v>4000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 성향에 대한 논쟁만 있을 뿐, 삼성전자 주가에 대한 실질적인 내용은 없음.</t>
+          <t>미국 광통신 관련주 급등에 따른 수혜 기대감과 함께, 물량 소화 및 매집 정황이 포착되며 2만 원대 돌파 전망이 제기됨.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['광통신', '수혜주', '매집']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1766000</v>
+        <v>253500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="G12" t="n">
-        <v>1695</v>
+        <v>1738</v>
       </c>
       <c r="H12" t="n">
-        <v>50.2</v>
+        <v>46.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1759000</v>
+        <v>253500</v>
       </c>
       <c r="K12" t="n">
-        <v>1770000</v>
+        <v>257000</v>
       </c>
       <c r="L12" t="n">
-        <v>1785000</v>
+        <v>259000</v>
       </c>
       <c r="M12" t="n">
-        <v>1735000</v>
+        <v>252000</v>
       </c>
       <c r="N12" t="n">
-        <v>50.2</v>
+        <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>3519311452000</v>
+        <v>2057724544750</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>333000</v>
+        <v>77100</v>
       </c>
       <c r="R12" t="n">
-        <v>-236000</v>
+        <v>-718000</v>
       </c>
       <c r="S12" t="n">
-        <v>-62000</v>
+        <v>-59000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>실적 시즌 도래 및 금리 인상 수혜 기대감. 단기적인 주가 변동성 언급.</t>
+          <t>정치 관련 주장과 함께 주가 조작 및 정치권의 반도체 산업 영향력에 대한 의문 제기. 특정 정치인 지지 또는 반대 의견 표출.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '금리인상', '수혜']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18630</v>
+        <v>1758000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.32%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>92</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>471</v>
       </c>
       <c r="G13" t="n">
-        <v>334</v>
+        <v>1709</v>
       </c>
       <c r="H13" t="n">
-        <v>10.85</v>
+        <v>50.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,152 +1607,152 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18570</v>
+        <v>1759000</v>
       </c>
       <c r="K13" t="n">
-        <v>18740</v>
+        <v>1770000</v>
       </c>
       <c r="L13" t="n">
-        <v>18900</v>
+        <v>1785000</v>
       </c>
       <c r="M13" t="n">
-        <v>18510</v>
+        <v>1735000</v>
       </c>
       <c r="N13" t="n">
-        <v>10.64</v>
+        <v>50.2</v>
       </c>
       <c r="O13" t="n">
-        <v>51878077925</v>
+        <v>3632106291000</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>333000</v>
       </c>
       <c r="R13" t="n">
-        <v>-287000</v>
+        <v>-242000</v>
       </c>
       <c r="S13" t="n">
-        <v>-76000</v>
+        <v>8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
+          <t>증시 상황과 관계없이 보유 유지 권유. 특정 정치인 및 경제 인사 언급과 함께 개인 투자자 주도 시장에 대한 의견 피력. 실적 시즌 및 금리 인상 수혜 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대규모계약', 'LNG', '대차해지']</t>
+          <t>['실적 시즌', '금리 인상', '보유']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16150</v>
+        <v>18555</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.31%</t>
+          <t>'-0.08%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.93</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>259</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>1366</v>
+        <v>340</v>
       </c>
       <c r="H14" t="n">
-        <v>4.88</v>
+        <v>10.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16100</v>
+        <v>18570</v>
       </c>
       <c r="K14" t="n">
-        <v>16200</v>
+        <v>18740</v>
       </c>
       <c r="L14" t="n">
-        <v>16750</v>
+        <v>18900</v>
       </c>
       <c r="M14" t="n">
-        <v>15560</v>
+        <v>18510</v>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>10.64</v>
       </c>
       <c r="O14" t="n">
-        <v>342306053095</v>
+        <v>52996666395</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-749000</v>
+        <v>-306000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>-77000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등에 따른 수혜 기대감과 함께, 물량 소화 및 매집 정황이 포착되며 2만 원대 돌파 전망이 제기됨.</t>
+          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', '수혜주', '매집']</t>
+          <t>['대규모계약', 'LNG', '대차해지']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8440</v>
+        <v>8420</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F15" t="n">
         <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>12744207715</v>
+        <v>13039788935</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1815,7 +1815,7 @@
         <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-335000</v>
+        <v>-236000</v>
       </c>
       <c r="S15" t="n">
         <v>-5000</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3465</v>
+        <v>13780</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.36%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.85</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
-        <v>315</v>
+        <v>389</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3520</v>
+        <v>13970</v>
       </c>
       <c r="K16" t="n">
-        <v>3730</v>
+        <v>13450</v>
       </c>
       <c r="L16" t="n">
-        <v>3750</v>
+        <v>13970</v>
       </c>
       <c r="M16" t="n">
-        <v>3420</v>
+        <v>13410</v>
       </c>
       <c r="N16" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5662272788</v>
+        <v>15661267705</v>
       </c>
       <c r="P16" t="n">
-        <v>16110</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>-317000</v>
+        <v>122000</v>
       </c>
       <c r="S16" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
+          <t>유가 변동성에 따른 단기 등락 예측. 후티 반군 관련 지정학적 리스크 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '차익실현']</t>
+          <t>['유가', '후티반군', '지정학적리스크']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13720</v>
+        <v>13310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.79%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>1.36</v>
       </c>
       <c r="E17" t="n">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>389</v>
+        <v>92</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>1.76</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13970</v>
+        <v>13530</v>
       </c>
       <c r="K17" t="n">
-        <v>13450</v>
+        <v>14280</v>
       </c>
       <c r="L17" t="n">
-        <v>13970</v>
+        <v>14800</v>
       </c>
       <c r="M17" t="n">
-        <v>13410</v>
+        <v>12960</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O17" t="n">
-        <v>15449958725</v>
+        <v>82685366515</v>
       </c>
       <c r="P17" t="n">
-        <v>36200</v>
+        <v>25700</v>
       </c>
       <c r="Q17" t="n">
-        <v>8920</v>
+        <v>4600</v>
       </c>
       <c r="R17" t="n">
-        <v>122000</v>
+        <v>-80000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유가 변동성에 따른 단기 등락 예측. 후티 반군 관련 지정학적 리스크 언급.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유가', '후티반군', '지정학적리스크']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13250</v>
+        <v>3460</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.36</v>
+        <v>-0.85</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>89</v>
+        <v>316</v>
       </c>
       <c r="H18" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13530</v>
+        <v>3520</v>
       </c>
       <c r="K18" t="n">
-        <v>14280</v>
+        <v>3730</v>
       </c>
       <c r="L18" t="n">
-        <v>14800</v>
+        <v>3750</v>
       </c>
       <c r="M18" t="n">
-        <v>12960</v>
+        <v>3420</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4</v>
+        <v>3.11</v>
       </c>
       <c r="O18" t="n">
-        <v>82408971465</v>
+        <v>5826874688</v>
       </c>
       <c r="P18" t="n">
-        <v>25700</v>
+        <v>16110</v>
       </c>
       <c r="Q18" t="n">
-        <v>4600</v>
+        <v>2300</v>
       </c>
       <c r="R18" t="n">
-        <v>-80000</v>
+        <v>-317000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>['상장폐지', '폭락', '차익실현']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10240</v>
+        <v>10200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-2.49%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
         <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H19" t="n">
         <v>18.42</v>
@@ -2174,7 +2174,7 @@
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>58627431695</v>
+        <v>58853416105</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2183,10 +2183,10 @@
         <v>1760</v>
       </c>
       <c r="R19" t="n">
-        <v>-39000</v>
+        <v>-70000</v>
       </c>
       <c r="S19" t="n">
-        <v>-5000</v>
+        <v>-6000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2234,13 +2234,13 @@
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F20" t="n">
         <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>50867959780</v>
+        <v>51395672442</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_14.xlsx
+++ b/data/trending_integrated_20260917_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.62%</t>
+          <t>'+21.47%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H2" t="n">
         <v>3.52</v>
@@ -610,7 +610,7 @@
         <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>52784379199</v>
+        <v>53512809504</v>
       </c>
       <c r="P2" t="n">
         <v>5140</v>
@@ -619,7 +619,7 @@
         <v>870</v>
       </c>
       <c r="R2" t="n">
-        <v>-32000</v>
+        <v>-58000</v>
       </c>
       <c r="S2" t="n">
         <v>-7000</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4545</v>
+        <v>4635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.36%</t>
+          <t>'+20.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="F3" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G3" t="n">
-        <v>1361</v>
+        <v>1433</v>
       </c>
       <c r="H3" t="n">
         <v>0.95</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>263193430083</v>
+        <v>269969388082</v>
       </c>
       <c r="P3" t="n">
         <v>6900</v>
@@ -711,14 +711,14 @@
         <v>1738</v>
       </c>
       <c r="R3" t="n">
-        <v>-150000</v>
+        <v>-138000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>카카오, 소프트뱅크 등 대형 기업의 인수 가능성이 언급되며 10배 상승에 대한 기대감 형성. 거래량 잠김 현상 확인.</t>
+          <t>카카오, 야후, 소프트뱅크의 잠재적 인수 가능성 및 인수가격 프리미엄 기대. 역사적 거래량 발생 및 10배 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수', '소프트뱅크', '텐버거']</t>
+          <t>['카카오', '소프트뱅크', '인수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21450</v>
+        <v>21550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.57%</t>
+          <t>'+16.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H4" t="n">
         <v>2.54</v>
@@ -794,7 +794,7 @@
         <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>289109711245</v>
+        <v>290542782395</v>
       </c>
       <c r="P4" t="n">
         <v>59600</v>
@@ -803,10 +803,10 @@
         <v>1030</v>
       </c>
       <c r="R4" t="n">
-        <v>-104000</v>
+        <v>-81000</v>
       </c>
       <c r="S4" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3825</v>
+        <v>3810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.29%</t>
+          <t>'+8.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,7 +857,7 @@
         <v>155</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
         <v>312</v>
@@ -886,7 +886,7 @@
         <v>8.06</v>
       </c>
       <c r="O5" t="n">
-        <v>95601681182</v>
+        <v>96335693789</v>
       </c>
       <c r="P5" t="n">
         <v>19950</v>
@@ -895,7 +895,7 @@
         <v>1913</v>
       </c>
       <c r="R5" t="n">
-        <v>-375000</v>
+        <v>-382000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -946,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H6" t="n">
         <v>3.71</v>
@@ -978,7 +978,7 @@
         <v>3.71</v>
       </c>
       <c r="O6" t="n">
-        <v>578332439</v>
+        <v>615081179</v>
       </c>
       <c r="P6" t="n">
         <v>901</v>
@@ -987,7 +987,7 @@
         <v>56</v>
       </c>
       <c r="R6" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21400</v>
+        <v>21450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.94%</t>
+          <t>'+6.19%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>78674603025</v>
+        <v>81224877775</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10420</v>
+        <v>10400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.51%</t>
+          <t>'+4.31%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F8" t="n">
         <v>83</v>
       </c>
       <c r="G8" t="n">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>177561300220</v>
+        <v>178073294990</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모치료제 관련 기대감 속 외인 매수세 유입. 예상 매출 1조 이상 전망.</t>
+          <t>낙태약 및 탈모 치료 수혜 기대감 속 개인 투자자 매수세 유입. 하지만 고점 거래량 및 제약사 사업 리스크 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료제', '외인매수']</t>
+          <t>['낙태약', '탈모치료', '수혜주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13400</v>
+        <v>13390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.72%</t>
+          <t>'+3.64%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>59195616790</v>
+        <v>59898917485</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1263,7 +1263,7 @@
         <v>3540</v>
       </c>
       <c r="R9" t="n">
-        <v>-58000</v>
+        <v>-100000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85800</v>
+        <v>85600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+2.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F10" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G10" t="n">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>114234734050</v>
+        <v>116681935200</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16140</v>
+        <v>16170</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.25%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>142</v>
       </c>
       <c r="G11" t="n">
-        <v>1380</v>
+        <v>1408</v>
       </c>
       <c r="H11" t="n">
         <v>4.88</v>
@@ -1438,7 +1438,7 @@
         <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>343407479465</v>
+        <v>345047706030</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1447,7 +1447,7 @@
         <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-749000</v>
+        <v>-686000</v>
       </c>
       <c r="S11" t="n">
         <v>4000</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253500</v>
+        <v>253000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="G12" t="n">
-        <v>1738</v>
+        <v>1730</v>
       </c>
       <c r="H12" t="n">
         <v>46.52</v>
@@ -1530,7 +1530,7 @@
         <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>2057724544750</v>
+        <v>2121170291750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1758000</v>
+        <v>18510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'-0.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>98</v>
       </c>
       <c r="F13" t="n">
-        <v>471</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>1709</v>
+        <v>355</v>
       </c>
       <c r="H13" t="n">
-        <v>50.2</v>
+        <v>10.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1759000</v>
+        <v>18570</v>
       </c>
       <c r="K13" t="n">
-        <v>1770000</v>
+        <v>18740</v>
       </c>
       <c r="L13" t="n">
-        <v>1785000</v>
+        <v>18900</v>
       </c>
       <c r="M13" t="n">
-        <v>1735000</v>
+        <v>18500</v>
       </c>
       <c r="N13" t="n">
-        <v>50.2</v>
+        <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>3632106291000</v>
+        <v>54758147205</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>333000</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-242000</v>
+        <v>-306000</v>
       </c>
       <c r="S13" t="n">
-        <v>8000</v>
+        <v>-77000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>증시 상황과 관계없이 보유 유지 권유. 특정 정치인 및 경제 인사 언급과 함께 개인 투자자 주도 시장에 대한 의견 피력. 실적 시즌 및 금리 인상 수혜 기대.</t>
+          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적 시즌', '금리 인상', '보유']</t>
+          <t>['대규모계약', 'LNG', '대차해지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18555</v>
+        <v>1751000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.08%</t>
+          <t>'-0.45%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>472</v>
       </c>
       <c r="G14" t="n">
-        <v>340</v>
+        <v>1704</v>
       </c>
       <c r="H14" t="n">
-        <v>10.85</v>
+        <v>50.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18570</v>
+        <v>1759000</v>
       </c>
       <c r="K14" t="n">
-        <v>18740</v>
+        <v>1770000</v>
       </c>
       <c r="L14" t="n">
-        <v>18900</v>
+        <v>1785000</v>
       </c>
       <c r="M14" t="n">
-        <v>18510</v>
+        <v>1735000</v>
       </c>
       <c r="N14" t="n">
-        <v>10.64</v>
+        <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>52996666395</v>
+        <v>3710480953000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>-306000</v>
+        <v>-242000</v>
       </c>
       <c r="S14" t="n">
-        <v>-77000</v>
+        <v>8000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
+          <t>증시 상황과 관계없이 보유 유지 권유. 특정 정치인 및 경제 인사 언급과 함께 개인 투자자 주도 시장에 대한 의견 피력. 실적 시즌 및 금리 인상 수혜 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대규모계약', 'LNG', '대차해지']</t>
+          <t>['실적 시즌', '금리 인상', '보유']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>13039788935</v>
+        <v>13112024810</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>3분기 실적 부진 및 4분기 전망 불확실성. 높은 부채 비율 및 증권사 목표가 하향 조정.</t>
+          <t>4분기 전망 및 중국 경쟁 심화 우려. 무능한 경영진과 높은 부채 비중, 목표가 하향 조정 등 악재 지속.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '부채', '전망']</t>
+          <t>['부채', '경쟁력', '목표가']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13780</v>
+        <v>13740</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.36%</t>
+          <t>'-1.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F16" t="n">
         <v>74</v>
       </c>
       <c r="G16" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>15661267705</v>
+        <v>15898903090</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13310</v>
+        <v>3460</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.36</v>
+        <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>92</v>
+        <v>317</v>
       </c>
       <c r="H17" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13530</v>
+        <v>3520</v>
       </c>
       <c r="K17" t="n">
-        <v>14280</v>
+        <v>3730</v>
       </c>
       <c r="L17" t="n">
-        <v>14800</v>
+        <v>3750</v>
       </c>
       <c r="M17" t="n">
-        <v>12960</v>
+        <v>3420</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4</v>
+        <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>82685366515</v>
+        <v>5865462763</v>
       </c>
       <c r="P17" t="n">
-        <v>25700</v>
+        <v>16110</v>
       </c>
       <c r="Q17" t="n">
-        <v>4600</v>
+        <v>2300</v>
       </c>
       <c r="R17" t="n">
-        <v>-80000</v>
+        <v>-328000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>['상장폐지', '폭락', '차익실현']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3460</v>
+        <v>13280</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.85%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.85</v>
+        <v>1.36</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>316</v>
+        <v>92</v>
       </c>
       <c r="H18" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3520</v>
+        <v>13530</v>
       </c>
       <c r="K18" t="n">
-        <v>3730</v>
+        <v>14280</v>
       </c>
       <c r="L18" t="n">
-        <v>3750</v>
+        <v>14800</v>
       </c>
       <c r="M18" t="n">
-        <v>3420</v>
+        <v>12960</v>
       </c>
       <c r="N18" t="n">
-        <v>3.11</v>
+        <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>5826874688</v>
+        <v>83049914340</v>
       </c>
       <c r="P18" t="n">
-        <v>16110</v>
+        <v>25700</v>
       </c>
       <c r="Q18" t="n">
-        <v>2300</v>
+        <v>4600</v>
       </c>
       <c r="R18" t="n">
-        <v>-317000</v>
+        <v>-66000</v>
       </c>
       <c r="S18" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '차익실현']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10200</v>
+        <v>10210</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.49%</t>
+          <t>'-2.39%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H19" t="n">
         <v>18.42</v>
@@ -2174,7 +2174,7 @@
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>58853416105</v>
+        <v>59113556505</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4135</v>
+        <v>4132</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.24%</t>
+          <t>'-6.30%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G20" t="n">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>51395672442</v>
+        <v>51665375332</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2275,7 +2275,7 @@
         <v>592</v>
       </c>
       <c r="R20" t="n">
-        <v>-161000</v>
+        <v>-162000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260917_14.xlsx
+++ b/data/trending_integrated_20260917_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1697</v>
+        <v>1684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.47%</t>
+          <t>'+20.54%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H2" t="n">
         <v>3.52</v>
@@ -610,7 +610,7 @@
         <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>53512809504</v>
+        <v>53849012494</v>
       </c>
       <c r="P2" t="n">
         <v>5140</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4635</v>
+        <v>4605</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.70%</t>
+          <t>'+19.92%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>588</v>
+        <v>610</v>
       </c>
       <c r="F3" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="G3" t="n">
-        <v>1433</v>
+        <v>1484</v>
       </c>
       <c r="H3" t="n">
         <v>0.95</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>269969388082</v>
+        <v>282183440038</v>
       </c>
       <c r="P3" t="n">
         <v>6900</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>카카오, 야후, 소프트뱅크의 잠재적 인수 가능성 및 인수가격 프리미엄 기대. 역사적 거래량 발생 및 10배 상승 가능성 언급.</t>
+          <t>카카오, 소프트뱅크 등 대기업 인수설 기반 급등. 높은 거래량 기록 및 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['카카오', '소프트뱅크', '인수']</t>
+          <t>['인수설', '거래량', '소프트뱅크']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21550</v>
+        <v>21300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.11%</t>
+          <t>'+14.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G4" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H4" t="n">
         <v>2.54</v>
@@ -794,7 +794,7 @@
         <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>290542782395</v>
+        <v>292574846670</v>
       </c>
       <c r="P4" t="n">
         <v>59600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3810</v>
+        <v>3840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.86%</t>
+          <t>'+9.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F5" t="n">
         <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H5" t="n">
         <v>8.01</v>
@@ -886,7 +886,7 @@
         <v>8.06</v>
       </c>
       <c r="O5" t="n">
-        <v>96335693789</v>
+        <v>96885143469</v>
       </c>
       <c r="P5" t="n">
         <v>19950</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>스페이스X 관련 투자 및 우주항공주 상승 기대감. 기관 및 기타 법인 매수세 유입.</t>
+          <t>스페이스X 관련주로 부각되며 상승 시도. 프로그램 매수세 및 기관 순매수 관찰.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['스페이스X', '우주항공', '매집']</t>
+          <t>['스페이스X', '우주항공주', '프로그램매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H6" t="n">
         <v>3.71</v>
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G7" t="n">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>81224877775</v>
+        <v>82106842950</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1130,13 +1130,13 @@
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>178073294990</v>
+        <v>178540650330</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13390</v>
+        <v>13380</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.64%</t>
+          <t>'+3.56%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>59898917485</v>
+        <v>60582608535</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85600</v>
+        <v>85500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F10" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G10" t="n">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>116681935200</v>
+        <v>119297317800</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 금리 인상 및 대미 투자와 관련된 긍정적 전망 제시. 원전 사업 관련 기대감.</t>
+          <t>AI 산업 성장 및 전력 수요 증가 전망에 따른 원전 관련주 부각. 대미 투자 및 금리 인상 변수 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['금리인상', '원전', '대미투자']</t>
+          <t>['원전', 'AI', '금리인상']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16170</v>
+        <v>16080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>260</v>
       </c>
       <c r="F11" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G11" t="n">
-        <v>1408</v>
+        <v>1425</v>
       </c>
       <c r="H11" t="n">
         <v>4.88</v>
@@ -1438,7 +1438,7 @@
         <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>345047706030</v>
+        <v>346750267115</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G12" t="n">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="H12" t="n">
         <v>46.52</v>
@@ -1530,7 +1530,7 @@
         <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>2121170291750</v>
+        <v>2167753328500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치 관련 주장과 함께 주가 조작 및 정치권의 반도체 산업 영향력에 대한 의문 제기. 특정 정치인 지지 또는 반대 의견 표출.</t>
+          <t>정치적 성향 관련 논쟁으로 인한 게시판 혼란. 주가 관련 객관적 분석 부재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18510</v>
+        <v>18460</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.32%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="H13" t="n">
         <v>10.85</v>
@@ -1616,13 +1616,13 @@
         <v>18900</v>
       </c>
       <c r="M13" t="n">
-        <v>18500</v>
+        <v>18450</v>
       </c>
       <c r="N13" t="n">
         <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>54758147205</v>
+        <v>56206571140</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1751000</v>
+        <v>1745000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.45%</t>
+          <t>'-0.80%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="G14" t="n">
-        <v>1704</v>
+        <v>1730</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3710480953000</v>
+        <v>3809921204000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>증시 상황과 관계없이 보유 유지 권유. 특정 정치인 및 경제 인사 언급과 함께 개인 투자자 주도 시장에 대한 의견 피력. 실적 시즌 및 금리 인상 수혜 기대.</t>
+          <t>실적 시즌 임박 및 일부 긍정적 전망 언급. 대만 증시 움직임 등 외부 요인 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적 시즌', '금리 인상', '보유']</t>
+          <t>['실적 시즌', '금리인상']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8420</v>
+        <v>8400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>13112024810</v>
+        <v>13834934870</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13740</v>
+        <v>3470</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.65%</t>
+          <t>'-1.42%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>391</v>
+        <v>319</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13970</v>
+        <v>3520</v>
       </c>
       <c r="K16" t="n">
-        <v>13450</v>
+        <v>3730</v>
       </c>
       <c r="L16" t="n">
-        <v>13970</v>
+        <v>3750</v>
       </c>
       <c r="M16" t="n">
-        <v>13410</v>
+        <v>3420</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O16" t="n">
-        <v>15898903090</v>
+        <v>5954131913</v>
       </c>
       <c r="P16" t="n">
-        <v>36200</v>
+        <v>16110</v>
       </c>
       <c r="Q16" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R16" t="n">
-        <v>122000</v>
+        <v>-328000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 변동성에 따른 단기 등락 예측. 후티 반군 관련 지정학적 리스크 언급.</t>
+          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유가', '후티반군', '지정학적리스크']</t>
+          <t>['상장폐지', '폭락', '차익실현']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3460</v>
+        <v>13720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.85</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>317</v>
+        <v>391</v>
       </c>
       <c r="H17" t="n">
-        <v>2.26</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3520</v>
+        <v>13970</v>
       </c>
       <c r="K17" t="n">
-        <v>3730</v>
+        <v>13450</v>
       </c>
       <c r="L17" t="n">
-        <v>3750</v>
+        <v>13970</v>
       </c>
       <c r="M17" t="n">
-        <v>3420</v>
+        <v>13410</v>
       </c>
       <c r="N17" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5865462763</v>
+        <v>16080333940</v>
       </c>
       <c r="P17" t="n">
-        <v>16110</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>2300</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>-328000</v>
+        <v>122000</v>
       </c>
       <c r="S17" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
+          <t>유가 변동성에 따른 단기 등락 예측. 후티 반군 관련 지정학적 리스크 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '차익실현']</t>
+          <t>['유가', '후티반군', '지정학적리스크']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13280</v>
+        <v>13230</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.85%</t>
+          <t>'-2.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.36</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
         <v>92</v>
@@ -2082,7 +2082,7 @@
         <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>83049914340</v>
+        <v>83226296210</v>
       </c>
       <c r="P18" t="n">
         <v>25700</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10210</v>
+        <v>10190</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-2.58%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H19" t="n">
         <v>18.42</v>
@@ -2174,7 +2174,7 @@
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>59113556505</v>
+        <v>59325753145</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4132</v>
+        <v>4130</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.30%</t>
+          <t>'-6.35%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G20" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>51665375332</v>
+        <v>51934813989</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_14.xlsx
+++ b/data/trending_integrated_20260917_14.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1684</v>
+        <v>4640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.54%</t>
+          <t>'+20.83%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>262</v>
       </c>
       <c r="G2" t="n">
-        <v>179</v>
+        <v>1563</v>
       </c>
       <c r="H2" t="n">
-        <v>3.52</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,91 +595,91 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1397</v>
+        <v>3840</v>
       </c>
       <c r="K2" t="n">
-        <v>1395</v>
+        <v>4170</v>
       </c>
       <c r="L2" t="n">
-        <v>1800</v>
+        <v>4800</v>
       </c>
       <c r="M2" t="n">
-        <v>1369</v>
+        <v>3990</v>
       </c>
       <c r="N2" t="n">
-        <v>3.57</v>
+        <v>1.03</v>
       </c>
       <c r="O2" t="n">
-        <v>53849012494</v>
+        <v>299198002584</v>
       </c>
       <c r="P2" t="n">
-        <v>5140</v>
+        <v>6900</v>
       </c>
       <c r="Q2" t="n">
-        <v>870</v>
+        <v>1738</v>
       </c>
       <c r="R2" t="n">
-        <v>-58000</v>
+        <v>-138000</v>
       </c>
       <c r="S2" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
+          <t>카카오, 소프트뱅크 등 대규모 투자 유치 가능성에 따른 텐배거 기대감. 역사적 거래량 기록 및 높은 상승 잠재력.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['우주', '스페이스X', '유상증자']</t>
+          <t>['카카오', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>321370</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4605</v>
+        <v>1686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.92%</t>
+          <t>'+20.69%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>610</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>252</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>1484</v>
+        <v>186</v>
       </c>
       <c r="H3" t="n">
-        <v>0.95</v>
+        <v>3.52</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,60 +687,60 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3840</v>
+        <v>1397</v>
       </c>
       <c r="K3" t="n">
-        <v>4170</v>
+        <v>1395</v>
       </c>
       <c r="L3" t="n">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="M3" t="n">
-        <v>3990</v>
+        <v>1369</v>
       </c>
       <c r="N3" t="n">
-        <v>1.03</v>
+        <v>3.57</v>
       </c>
       <c r="O3" t="n">
-        <v>282183440038</v>
+        <v>54486502480</v>
       </c>
       <c r="P3" t="n">
-        <v>6900</v>
+        <v>5140</v>
       </c>
       <c r="Q3" t="n">
-        <v>1738</v>
+        <v>870</v>
       </c>
       <c r="R3" t="n">
-        <v>-138000</v>
+        <v>-58000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>카카오, 소프트뱅크 등 대기업 인수설 기반 급등. 높은 거래량 기록 및 추가 상승 기대.</t>
+          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수설', '거래량', '소프트뱅크']</t>
+          <t>['우주', '스페이스X', '유상증자']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>321370</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21300</v>
+        <v>21450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.76%</t>
+          <t>'+15.57%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
         <v>77</v>
       </c>
       <c r="G4" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H4" t="n">
         <v>2.54</v>
@@ -794,7 +794,7 @@
         <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>292574846670</v>
+        <v>296156021545</v>
       </c>
       <c r="P4" t="n">
         <v>59600</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3840</v>
+        <v>3870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.71%</t>
+          <t>'+10.57%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H5" t="n">
         <v>8.01</v>
@@ -886,7 +886,7 @@
         <v>8.06</v>
       </c>
       <c r="O5" t="n">
-        <v>96885143469</v>
+        <v>97758598525</v>
       </c>
       <c r="P5" t="n">
         <v>19950</v>
@@ -946,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="H6" t="n">
         <v>3.71</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>부채 규모와 거래 규칙 변경에 대한 언급. 100원 돌파 및 300원 이상 상승에 대한 기대. 회사 문제 없음에도 걱정하는 시각에 대한 반론. 방산용 AR 디스플레이 양산 협력 신사업 발표.</t>
+          <t>방산용 AR 디스플레이 양산 협력 등 신사업 본격화. 차익 실현 및 단기 급등 가능성, 투자 주의 요구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['신사업', 'AR 디스플레이', '양산 협력']</t>
+          <t>['AR디스플레이', '신사업']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21450</v>
+        <v>21400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.19%</t>
+          <t>'+5.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>141</v>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>82106842950</v>
+        <v>83722675450</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등과 연계된 긍정적 전망. 금리 인상에도 불구하고 장기 보유 시 수익 기대. 공매도 세력에 대한 경계와 함께 수주 가능성 언급. 60일선 돌파 및 추세 전환 기대.</t>
+          <t>나스닥 반등, 공매도 세력과의 수급 싸움, 수주 기대감에 따른 단기 상승 전망. 다만, 변동성 고려 필요.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['추세 전환', '공매도', '수주']</t>
+          <t>['나스닥', '공매도', '수주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10400</v>
+        <v>10430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.31%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>178540650330</v>
+        <v>178986583030</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료 수혜 기대감 속 개인 투자자 매수세 유입. 하지만 고점 거래량 및 제약사 사업 리스크 언급.</t>
+          <t>낙태약 및 탈모 치료제 관련 기대감 속에서 거래량 동반 상승 전망. 그러나 객관적 근거는 부족.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '수혜주']</t>
+          <t>['낙태약', '탈모치료']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13380</v>
+        <v>13370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.56%</t>
+          <t>'+3.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
         <v>484</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>60582608535</v>
+        <v>61247853535</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1314,13 +1314,13 @@
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F10" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G10" t="n">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>119297317800</v>
+        <v>123399005350</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16080</v>
+        <v>16100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F11" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G11" t="n">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="H11" t="n">
         <v>4.88</v>
@@ -1438,7 +1438,7 @@
         <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>346750267115</v>
+        <v>349795151660</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253000</v>
+        <v>252500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'-0.39%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="G12" t="n">
-        <v>1728</v>
+        <v>1750</v>
       </c>
       <c r="H12" t="n">
         <v>46.52</v>
@@ -1530,7 +1530,7 @@
         <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>2167753328500</v>
+        <v>2243851963750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 성향 관련 논쟁으로 인한 게시판 혼란. 주가 관련 객관적 분석 부재.</t>
+          <t>정치적 논쟁으로 인한 종목 관련 게시글의 신뢰도 저하. 객관적 분석이나 팩트 부재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1590,13 +1590,13 @@
         <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" t="n">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="H13" t="n">
         <v>10.85</v>
@@ -1616,13 +1616,13 @@
         <v>18900</v>
       </c>
       <c r="M13" t="n">
-        <v>18450</v>
+        <v>18400</v>
       </c>
       <c r="N13" t="n">
         <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>56206571140</v>
+        <v>58092034985</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1745000</v>
+        <v>1747000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.80%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G14" t="n">
-        <v>1730</v>
+        <v>1709</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3809921204000</v>
+        <v>3914820086500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 시즌 임박 및 일부 긍정적 전망 언급. 대만 증시 움직임 등 외부 요인 언급.</t>
+          <t>실적 시즌 진입 및 금리 인상 수혜 기대감 속 홀딩 권유. 단기적 등락 가능성 및 투자 주체별 전략 필요.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적 시즌', '금리인상']</t>
+          <t>['실적', '금리인상']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8400</v>
+        <v>8390</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F15" t="n">
         <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>13834934870</v>
+        <v>14550080670</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1872,7 +1872,7 @@
         <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H16" t="n">
         <v>2.26</v>
@@ -1898,7 +1898,7 @@
         <v>3.11</v>
       </c>
       <c r="O16" t="n">
-        <v>5954131913</v>
+        <v>6015195148</v>
       </c>
       <c r="P16" t="n">
         <v>16110</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13720</v>
+        <v>13330</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.79%</t>
+          <t>'-1.48%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>1.36</v>
       </c>
       <c r="E17" t="n">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>391</v>
+        <v>93</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>1.76</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13970</v>
+        <v>13530</v>
       </c>
       <c r="K17" t="n">
-        <v>13450</v>
+        <v>14280</v>
       </c>
       <c r="L17" t="n">
-        <v>13970</v>
+        <v>14800</v>
       </c>
       <c r="M17" t="n">
-        <v>13410</v>
+        <v>12960</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O17" t="n">
-        <v>16080333940</v>
+        <v>83486291630</v>
       </c>
       <c r="P17" t="n">
-        <v>36200</v>
+        <v>25700</v>
       </c>
       <c r="Q17" t="n">
-        <v>8920</v>
+        <v>4600</v>
       </c>
       <c r="R17" t="n">
-        <v>122000</v>
+        <v>-66000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유가 변동성에 따른 단기 등락 예측. 후티 반군 관련 지정학적 리스크 언급.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유가', '후티반군', '지정학적리스크']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13230</v>
+        <v>13740</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.22%</t>
+          <t>'-1.65%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.36</v>
+        <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G18" t="n">
-        <v>92</v>
+        <v>389</v>
       </c>
       <c r="H18" t="n">
-        <v>1.76</v>
+        <v>0.01</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,60 +2067,60 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13530</v>
+        <v>13970</v>
       </c>
       <c r="K18" t="n">
-        <v>14280</v>
+        <v>13450</v>
       </c>
       <c r="L18" t="n">
-        <v>14800</v>
+        <v>13970</v>
       </c>
       <c r="M18" t="n">
-        <v>12960</v>
+        <v>13410</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>83226296210</v>
+        <v>16327678290</v>
       </c>
       <c r="P18" t="n">
-        <v>25700</v>
+        <v>36200</v>
       </c>
       <c r="Q18" t="n">
-        <v>4600</v>
+        <v>8920</v>
       </c>
       <c r="R18" t="n">
-        <v>-66000</v>
+        <v>122000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>유가 변동성 및 지정학적 리스크에 따른 주가 등락. 외국인 매수세와 프로그램 매도 공존.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>['유가', '지정학적 리스크', '외국인']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10190</v>
+        <v>10160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.58%</t>
+          <t>'-2.87%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H19" t="n">
         <v>18.42</v>
@@ -2174,7 +2174,7 @@
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>59325753145</v>
+        <v>59867966175</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2223,18 +2223,18 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4130</v>
+        <v>4125</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.35%</t>
+          <t>'-6.46%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" t="n">
         <v>59</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>51934813989</v>
+        <v>52227263666</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
